--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G11">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G27">

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11">

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Widad Témara</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Moghreb Tétouan</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Widad Témara</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Moghreb Tétouan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G19">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G25">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G27">

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Widad Témara</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Moghreb Tétouan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Widad Témara</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Moghreb Tétouan</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G19">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G27">

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G27">

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Widad Témara</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Widad Témara</t>
         </is>
       </c>
       <c r="G19">

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11">

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Widad Témara</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Widad Témara</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G19">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G27">

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Moghreb Tétouan</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Widad Témara</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Moghreb Tétouan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Widad Témara</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G19">

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU29"/>
+  <dimension ref="A1:AU25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Amal Tiznit</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Moghreb Tétouan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G15">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G16">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G17">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Widad Témara</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G18">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Moghreb Tétouan</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G23">
@@ -4174,27 +4174,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-09-23 21:00:00</t>
+          <t>2026-09-23 22:30:00</t>
         </is>
       </c>
     </row>
@@ -4337,27 +4337,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G25">
@@ -4487,658 +4487,6 @@
         <v>0</v>
       </c>
       <c r="AU25" t="inlineStr">
-        <is>
-          <t>2026-09-23 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Métlaoui</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Zarzis</t>
-        </is>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
-        <v>0</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>0</v>
-      </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="W26">
-        <v>0</v>
-      </c>
-      <c r="X26">
-        <v>0</v>
-      </c>
-      <c r="Y26">
-        <v>0</v>
-      </c>
-      <c r="Z26">
-        <v>0</v>
-      </c>
-      <c r="AA26">
-        <v>0</v>
-      </c>
-      <c r="AB26">
-        <v>0</v>
-      </c>
-      <c r="AC26">
-        <v>0</v>
-      </c>
-      <c r="AD26">
-        <v>0</v>
-      </c>
-      <c r="AE26">
-        <v>0</v>
-      </c>
-      <c r="AF26">
-        <v>0</v>
-      </c>
-      <c r="AG26">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>0</v>
-      </c>
-      <c r="AK26">
-        <v>0</v>
-      </c>
-      <c r="AL26">
-        <v>0</v>
-      </c>
-      <c r="AM26">
-        <v>-1</v>
-      </c>
-      <c r="AN26">
-        <v>-1</v>
-      </c>
-      <c r="AO26">
-        <v>-1</v>
-      </c>
-      <c r="AP26">
-        <v>-1</v>
-      </c>
-      <c r="AQ26">
-        <v>0</v>
-      </c>
-      <c r="AR26">
-        <v>0</v>
-      </c>
-      <c r="AS26">
-        <v>0</v>
-      </c>
-      <c r="AT26">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>2026-09-23 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>ES Tunis</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Monastir</t>
-        </is>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
-        <v>0</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>0</v>
-      </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27">
-        <v>0</v>
-      </c>
-      <c r="Y27">
-        <v>0</v>
-      </c>
-      <c r="Z27">
-        <v>0</v>
-      </c>
-      <c r="AA27">
-        <v>0</v>
-      </c>
-      <c r="AB27">
-        <v>0</v>
-      </c>
-      <c r="AC27">
-        <v>0</v>
-      </c>
-      <c r="AD27">
-        <v>0</v>
-      </c>
-      <c r="AE27">
-        <v>0</v>
-      </c>
-      <c r="AF27">
-        <v>0</v>
-      </c>
-      <c r="AG27">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>0</v>
-      </c>
-      <c r="AK27">
-        <v>0</v>
-      </c>
-      <c r="AL27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>-1</v>
-      </c>
-      <c r="AN27">
-        <v>-1</v>
-      </c>
-      <c r="AO27">
-        <v>-1</v>
-      </c>
-      <c r="AP27">
-        <v>-1</v>
-      </c>
-      <c r="AQ27">
-        <v>0</v>
-      </c>
-      <c r="AR27">
-        <v>0</v>
-      </c>
-      <c r="AS27">
-        <v>0</v>
-      </c>
-      <c r="AT27">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>2026-09-23 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Seattle Sounders</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Real Salt Lake</t>
-        </is>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N28">
-        <v>1.63</v>
-      </c>
-      <c r="O28">
-        <v>4.26</v>
-      </c>
-      <c r="P28">
-        <v>5.45</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>0</v>
-      </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
-      <c r="W28">
-        <v>0</v>
-      </c>
-      <c r="X28">
-        <v>0</v>
-      </c>
-      <c r="Y28">
-        <v>0</v>
-      </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-      <c r="AA28">
-        <v>1.7</v>
-      </c>
-      <c r="AB28">
-        <v>2</v>
-      </c>
-      <c r="AC28">
-        <v>0</v>
-      </c>
-      <c r="AD28">
-        <v>0</v>
-      </c>
-      <c r="AE28">
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <v>0</v>
-      </c>
-      <c r="AG28">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>0</v>
-      </c>
-      <c r="AK28">
-        <v>0</v>
-      </c>
-      <c r="AL28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
-        <v>-1</v>
-      </c>
-      <c r="AN28">
-        <v>-1</v>
-      </c>
-      <c r="AO28">
-        <v>-1</v>
-      </c>
-      <c r="AP28">
-        <v>-1</v>
-      </c>
-      <c r="AQ28">
-        <v>0</v>
-      </c>
-      <c r="AR28">
-        <v>0</v>
-      </c>
-      <c r="AS28">
-        <v>0</v>
-      </c>
-      <c r="AT28">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>2026-09-23 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Vancouver FC</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>York9 FC</t>
-        </is>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
-      <c r="Q29">
-        <v>0</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
-      <c r="U29">
-        <v>0</v>
-      </c>
-      <c r="V29">
-        <v>0</v>
-      </c>
-      <c r="W29">
-        <v>0</v>
-      </c>
-      <c r="X29">
-        <v>0</v>
-      </c>
-      <c r="Y29">
-        <v>0</v>
-      </c>
-      <c r="Z29">
-        <v>0</v>
-      </c>
-      <c r="AA29">
-        <v>0</v>
-      </c>
-      <c r="AB29">
-        <v>0</v>
-      </c>
-      <c r="AC29">
-        <v>0</v>
-      </c>
-      <c r="AD29">
-        <v>0</v>
-      </c>
-      <c r="AE29">
-        <v>0</v>
-      </c>
-      <c r="AF29">
-        <v>0</v>
-      </c>
-      <c r="AG29">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>0</v>
-      </c>
-      <c r="AK29">
-        <v>0</v>
-      </c>
-      <c r="AL29">
-        <v>0</v>
-      </c>
-      <c r="AM29">
-        <v>-1</v>
-      </c>
-      <c r="AN29">
-        <v>-1</v>
-      </c>
-      <c r="AO29">
-        <v>-1</v>
-      </c>
-      <c r="AP29">
-        <v>-1</v>
-      </c>
-      <c r="AQ29">
-        <v>0</v>
-      </c>
-      <c r="AR29">
-        <v>0</v>
-      </c>
-      <c r="AS29">
-        <v>0</v>
-      </c>
-      <c r="AT29">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
         <is>
           <t>2026-09-23 23:00:00</t>
         </is>

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU25"/>
+  <dimension ref="A1:AU22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G12">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G13">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G14">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Moghreb Tétouan</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G20">
@@ -3685,27 +3685,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-09-23 21:00:00</t>
+          <t>2026-09-23 22:30:00</t>
         </is>
       </c>
     </row>
@@ -3848,27 +3848,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G22">
@@ -3998,495 +3998,6 @@
         <v>0</v>
       </c>
       <c r="AU22" t="inlineStr">
-        <is>
-          <t>2026-09-23 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>ES Tunis</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Monastir</t>
-        </is>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>0</v>
-      </c>
-      <c r="Y23">
-        <v>0</v>
-      </c>
-      <c r="Z23">
-        <v>0</v>
-      </c>
-      <c r="AA23">
-        <v>0</v>
-      </c>
-      <c r="AB23">
-        <v>0</v>
-      </c>
-      <c r="AC23">
-        <v>0</v>
-      </c>
-      <c r="AD23">
-        <v>0</v>
-      </c>
-      <c r="AE23">
-        <v>0</v>
-      </c>
-      <c r="AF23">
-        <v>0</v>
-      </c>
-      <c r="AG23">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>0</v>
-      </c>
-      <c r="AK23">
-        <v>0</v>
-      </c>
-      <c r="AL23">
-        <v>0</v>
-      </c>
-      <c r="AM23">
-        <v>-1</v>
-      </c>
-      <c r="AN23">
-        <v>-1</v>
-      </c>
-      <c r="AO23">
-        <v>-1</v>
-      </c>
-      <c r="AP23">
-        <v>-1</v>
-      </c>
-      <c r="AQ23">
-        <v>0</v>
-      </c>
-      <c r="AR23">
-        <v>0</v>
-      </c>
-      <c r="AS23">
-        <v>0</v>
-      </c>
-      <c r="AT23">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>2026-09-23 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Seattle Sounders</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Real Salt Lake</t>
-        </is>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N24">
-        <v>1.63</v>
-      </c>
-      <c r="O24">
-        <v>4.26</v>
-      </c>
-      <c r="P24">
-        <v>5.45</v>
-      </c>
-      <c r="Q24">
-        <v>0</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-      <c r="U24">
-        <v>0</v>
-      </c>
-      <c r="V24">
-        <v>0</v>
-      </c>
-      <c r="W24">
-        <v>0</v>
-      </c>
-      <c r="X24">
-        <v>0</v>
-      </c>
-      <c r="Y24">
-        <v>0</v>
-      </c>
-      <c r="Z24">
-        <v>0</v>
-      </c>
-      <c r="AA24">
-        <v>1.7</v>
-      </c>
-      <c r="AB24">
-        <v>2</v>
-      </c>
-      <c r="AC24">
-        <v>0</v>
-      </c>
-      <c r="AD24">
-        <v>0</v>
-      </c>
-      <c r="AE24">
-        <v>0</v>
-      </c>
-      <c r="AF24">
-        <v>0</v>
-      </c>
-      <c r="AG24">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>0</v>
-      </c>
-      <c r="AK24">
-        <v>0</v>
-      </c>
-      <c r="AL24">
-        <v>0</v>
-      </c>
-      <c r="AM24">
-        <v>-1</v>
-      </c>
-      <c r="AN24">
-        <v>-1</v>
-      </c>
-      <c r="AO24">
-        <v>-1</v>
-      </c>
-      <c r="AP24">
-        <v>-1</v>
-      </c>
-      <c r="AQ24">
-        <v>0</v>
-      </c>
-      <c r="AR24">
-        <v>0</v>
-      </c>
-      <c r="AS24">
-        <v>0</v>
-      </c>
-      <c r="AT24">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>2026-09-23 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Vancouver FC</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>York9 FC</t>
-        </is>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>0</v>
-      </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
-      <c r="W25">
-        <v>0</v>
-      </c>
-      <c r="X25">
-        <v>0</v>
-      </c>
-      <c r="Y25">
-        <v>0</v>
-      </c>
-      <c r="Z25">
-        <v>0</v>
-      </c>
-      <c r="AA25">
-        <v>0</v>
-      </c>
-      <c r="AB25">
-        <v>0</v>
-      </c>
-      <c r="AC25">
-        <v>0</v>
-      </c>
-      <c r="AD25">
-        <v>0</v>
-      </c>
-      <c r="AE25">
-        <v>0</v>
-      </c>
-      <c r="AF25">
-        <v>0</v>
-      </c>
-      <c r="AG25">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>0</v>
-      </c>
-      <c r="AK25">
-        <v>0</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>-1</v>
-      </c>
-      <c r="AN25">
-        <v>-1</v>
-      </c>
-      <c r="AO25">
-        <v>-1</v>
-      </c>
-      <c r="AP25">
-        <v>-1</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25">
-        <v>0</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
         <is>
           <t>2026-09-23 23:00:00</t>
         </is>

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="O21">
-        <v>4.26</v>
+        <v>2.3</v>
       </c>
       <c r="P21">
-        <v>5.45</v>
+        <v>4.75</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
         <v>0</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="AA21">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AB21">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL21">
         <v>0</v>

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -644,55 +644,55 @@
         <v>3.8</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -3741,10 +3741,10 @@
         <v>4.75</v>
       </c>
       <c r="Q21">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R21">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S21">
         <v>1.25</v>
@@ -3759,7 +3759,7 @@
         <v>1.58</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X21">
         <v>0</v>
@@ -3768,19 +3768,19 @@
         <v>1.17</v>
       </c>
       <c r="Z21">
-        <v>5.01</v>
+        <v>4.6</v>
       </c>
       <c r="AA21">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB21">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AC21">
         <v>2.28</v>
       </c>
       <c r="AD21">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AE21">
         <v>1.18</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AL21">
         <v>0</v>

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="O2">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P2">
         <v>3.8</v>
       </c>
       <c r="Q2">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R2">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="S2">
         <v>1.21</v>
@@ -656,43 +656,43 @@
         <v>3.58</v>
       </c>
       <c r="U2">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="V2">
         <v>1.62</v>
       </c>
       <c r="W2">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z2">
-        <v>5.05</v>
+        <v>4.95</v>
       </c>
       <c r="AA2">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB2">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="AC2">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AD2">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE2">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF2">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AG2">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK2">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -3741,22 +3741,22 @@
         <v>4.75</v>
       </c>
       <c r="Q21">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R21">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T21">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U21">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="V21">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W21">
         <v>1.13</v>
@@ -3765,19 +3765,19 @@
         <v>0</v>
       </c>
       <c r="Y21">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z21">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AA21">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AB21">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="AC21">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="AD21">
         <v>1.54</v>
@@ -3786,10 +3786,10 @@
         <v>1.18</v>
       </c>
       <c r="AF21">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG21">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK21">
         <v>1.84</v>

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="O2">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P2">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="Q2">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="R2">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S2">
         <v>1.21</v>
@@ -689,7 +689,7 @@
         <v>1.2</v>
       </c>
       <c r="AF2">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG2">
         <v>2.45</v>
@@ -708,7 +708,7 @@
         <v>1.17</v>
       </c>
       <c r="AK2">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL2">
         <v>0</v>

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -3741,7 +3741,7 @@
         <v>4.75</v>
       </c>
       <c r="Q21">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="R21">
         <v>2.32</v>
@@ -3753,13 +3753,13 @@
         <v>3.6</v>
       </c>
       <c r="U21">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="V21">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W21">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
         <v>0</v>
@@ -3771,13 +3771,13 @@
         <v>5</v>
       </c>
       <c r="AA21">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB21">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AC21">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AD21">
         <v>1.54</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AL21">
         <v>0</v>

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="O2">
         <v>3.7</v>
       </c>
       <c r="P2">
-        <v>3.83</v>
+        <v>3.58</v>
       </c>
       <c r="Q2">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="R2">
         <v>2.4</v>
@@ -659,7 +659,7 @@
         <v>2.13</v>
       </c>
       <c r="V2">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W2">
         <v>1.17</v>
@@ -689,7 +689,7 @@
         <v>1.2</v>
       </c>
       <c r="AF2">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG2">
         <v>2.45</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK2">
         <v>2</v>

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -2261,7 +2261,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N12">

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="O2">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="P2">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="Q2">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="R2">
         <v>2.4</v>
@@ -689,10 +689,10 @@
         <v>1.2</v>
       </c>
       <c r="AF2">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AG2">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -635,31 +635,31 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="O2">
         <v>3.95</v>
       </c>
       <c r="P2">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="Q2">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="R2">
         <v>2.4</v>
       </c>
       <c r="S2">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T2">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="U2">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="V2">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W2">
         <v>1.17</v>
@@ -668,31 +668,31 @@
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z2">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="AA2">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AB2">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="AC2">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD2">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE2">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF2">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AG2">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK2">
         <v>2</v>
@@ -3744,19 +3744,19 @@
         <v>2.43</v>
       </c>
       <c r="R21">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S21">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U21">
         <v>2.36</v>
       </c>
       <c r="V21">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W21">
         <v>1.11</v>
@@ -3777,16 +3777,16 @@
         <v>2.35</v>
       </c>
       <c r="AC21">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AD21">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE21">
         <v>1.18</v>
       </c>
       <c r="AF21">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG21">
         <v>2.4</v>

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -2424,7 +2424,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N13">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N14">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G16">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G17">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N17">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N18">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N19">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N20">

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -638,16 +638,16 @@
         <v>1.75</v>
       </c>
       <c r="O2">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="P2">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="Q2">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="R2">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="S2">
         <v>1.2</v>
@@ -656,28 +656,28 @@
         <v>3.68</v>
       </c>
       <c r="U2">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="V2">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W2">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z2">
         <v>5.1</v>
       </c>
       <c r="AA2">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AB2">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AC2">
         <v>2.15</v>

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -3741,31 +3741,31 @@
         <v>4.75</v>
       </c>
       <c r="Q21">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="R21">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T21">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U21">
-        <v>2.36</v>
+        <v>2.21</v>
       </c>
       <c r="V21">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W21">
         <v>1.11</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z21">
         <v>5</v>
@@ -3777,16 +3777,16 @@
         <v>2.35</v>
       </c>
       <c r="AC21">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AD21">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE21">
         <v>1.18</v>
       </c>
       <c r="AF21">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AG21">
         <v>2.4</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK21">
         <v>1.83</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC22">
         <v>0</v>

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -638,34 +638,34 @@
         <v>1.75</v>
       </c>
       <c r="O2">
-        <v>3.86</v>
+        <v>3.7</v>
       </c>
       <c r="P2">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="Q2">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="R2">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="S2">
         <v>1.2</v>
       </c>
       <c r="T2">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="U2">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="V2">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W2">
         <v>1.13</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
         <v>1.1</v>
@@ -677,7 +677,7 @@
         <v>1.5</v>
       </c>
       <c r="AB2">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AC2">
         <v>2.15</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK2">
         <v>2</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O22">
         <v>3.7</v>
       </c>
       <c r="P22">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB22">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AC22">
         <v>0</v>

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -638,31 +638,31 @@
         <v>1.75</v>
       </c>
       <c r="O2">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P2">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q2">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R2">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="S2">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T2">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="U2">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="V2">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W2">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X2">
         <v>1.01</v>
@@ -671,28 +671,28 @@
         <v>1.1</v>
       </c>
       <c r="Z2">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="AA2">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AB2">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="AC2">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AD2">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AE2">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF2">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG2">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.18</v>
       </c>
       <c r="AK2">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="O3">
         <v>4</v>
       </c>
       <c r="P3">
-        <v>5.54</v>
+        <v>5.5</v>
       </c>
       <c r="Q3">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R3">
         <v>2.27</v>
@@ -819,13 +819,13 @@
         <v>3.12</v>
       </c>
       <c r="U3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="V3">
         <v>1.46</v>
       </c>
       <c r="W3">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X3">
         <v>1.01</v>
@@ -834,28 +834,28 @@
         <v>1.19</v>
       </c>
       <c r="Z3">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AA3">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AB3">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC3">
         <v>2.88</v>
       </c>
       <c r="AD3">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE3">
         <v>1.11</v>
       </c>
       <c r="AF3">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG3">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.14</v>
       </c>
       <c r="AK3">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -635,34 +635,34 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O2">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P2">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q2">
         <v>2.1</v>
       </c>
       <c r="R2">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="S2">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T2">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="U2">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="V2">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W2">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X2">
         <v>1.01</v>
@@ -671,19 +671,19 @@
         <v>1.1</v>
       </c>
       <c r="Z2">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="AA2">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AB2">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="AC2">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AD2">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AE2">
         <v>1.21</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK2">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="O22">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P22">
+        <v>3.18</v>
+      </c>
+      <c r="Q22">
+        <v>2.25</v>
+      </c>
+      <c r="R22">
+        <v>2.45</v>
+      </c>
+      <c r="S22">
+        <v>1.25</v>
+      </c>
+      <c r="T22">
         <v>3.6</v>
       </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA22">
+        <v>1.57</v>
+      </c>
+      <c r="AB22">
+        <v>2.21</v>
+      </c>
+      <c r="AC22">
+        <v>2.34</v>
+      </c>
+      <c r="AD22">
+        <v>1.51</v>
+      </c>
+      <c r="AE22">
+        <v>1.15</v>
+      </c>
+      <c r="AF22">
         <v>1.5</v>
       </c>
-      <c r="AB22">
-        <v>2.5</v>
-      </c>
-      <c r="AC22">
-        <v>0</v>
-      </c>
-      <c r="AD22">
-        <v>0</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <v>0</v>
-      </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL22">
         <v>0</v>

--- a/jogos_2026-09-23.xlsx
+++ b/jogos_2026-09-23.xlsx
@@ -612,130 +612,130 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
+        <v>1.53</v>
+      </c>
+      <c r="O2">
+        <v>4.3</v>
+      </c>
+      <c r="P2">
+        <v>5</v>
+      </c>
+      <c r="Q2">
+        <v>1.85</v>
+      </c>
+      <c r="R2">
+        <v>2.6</v>
+      </c>
+      <c r="S2">
+        <v>1.17</v>
+      </c>
+      <c r="T2">
+        <v>4</v>
+      </c>
+      <c r="U2">
+        <v>2.11</v>
+      </c>
+      <c r="V2">
         <v>1.73</v>
       </c>
-      <c r="O2">
-        <v>3.85</v>
-      </c>
-      <c r="P2">
-        <v>4</v>
-      </c>
-      <c r="Q2">
-        <v>2.1</v>
-      </c>
-      <c r="R2">
-        <v>2.44</v>
-      </c>
-      <c r="S2">
-        <v>1.2</v>
-      </c>
-      <c r="T2">
-        <v>3.68</v>
-      </c>
-      <c r="U2">
-        <v>2.21</v>
-      </c>
-      <c r="V2">
-        <v>1.67</v>
-      </c>
       <c r="W2">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X2">
         <v>1.01</v>
       </c>
       <c r="Y2">
+        <v>1.08</v>
+      </c>
+      <c r="Z2">
+        <v>5.7</v>
+      </c>
+      <c r="AA2">
+        <v>1.43</v>
+      </c>
+      <c r="AB2">
+        <v>2.83</v>
+      </c>
+      <c r="AC2">
+        <v>2.09</v>
+      </c>
+      <c r="AD2">
+        <v>1.69</v>
+      </c>
+      <c r="AE2">
+        <v>1.26</v>
+      </c>
+      <c r="AF2">
+        <v>1.5</v>
+      </c>
+      <c r="AG2">
+        <v>2.4</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>["14", "48", "84", "90+2"]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2">
         <v>1.1</v>
       </c>
-      <c r="Z2">
-        <v>5.1</v>
-      </c>
-      <c r="AA2">
-        <v>1.48</v>
-      </c>
-      <c r="AB2">
-        <v>2.64</v>
-      </c>
-      <c r="AC2">
-        <v>2.26</v>
-      </c>
-      <c r="AD2">
-        <v>1.6</v>
-      </c>
-      <c r="AE2">
-        <v>1.21</v>
-      </c>
-      <c r="AF2">
-        <v>1.44</v>
-      </c>
-      <c r="AG2">
-        <v>2.63</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2">
-        <v>1.16</v>
-      </c>
       <c r="AK2">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -787,118 +787,118 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="O3">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>5.5</v>
+        <v>4.78</v>
       </c>
       <c r="Q3">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R3">
-        <v>2.27</v>
+        <v>2.14</v>
       </c>
       <c r="S3">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>3.12</v>
+        <v>2.86</v>
       </c>
       <c r="U3">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V3">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z3">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AA3">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB3">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC3">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AD3">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE3">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF3">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AG3">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
+          <t>["72"]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ3">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK3">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -3747,49 +3747,49 @@
         <v>2.4</v>
       </c>
       <c r="S21">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T21">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U21">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="V21">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z21">
         <v>5</v>
       </c>
       <c r="AA21">
+        <v>1.49</v>
+      </c>
+      <c r="AB21">
+        <v>2.4</v>
+      </c>
+      <c r="AC21">
+        <v>2.21</v>
+      </c>
+      <c r="AD21">
         <v>1.57</v>
       </c>
-      <c r="AB21">
-        <v>2.35</v>
-      </c>
-      <c r="AC21">
-        <v>2.29</v>
-      </c>
-      <c r="AD21">
-        <v>1.53</v>
-      </c>
       <c r="AE21">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF21">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG21">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK21">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,28 +3904,28 @@
         <v>3.18</v>
       </c>
       <c r="Q22">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R22">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T22">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U22">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="V22">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W22">
         <v>1.13</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
         <v>1.15</v>
@@ -3934,25 +3934,25 @@
         <v>4.8</v>
       </c>
       <c r="AA22">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB22">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="AC22">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="AD22">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE22">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF22">
         <v>1.5</v>
       </c>
       <c r="AG22">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK22">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL22">
         <v>0</v>
